--- a/夏休みの課題/進捗コスト表.xlsx
+++ b/夏休みの課題/進捗コスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fko2347025\Desktop\MeteorFighters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Documents\GitHub\summer\夏休みの課題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{755897E3-F2C4-4A14-ACF3-805A4F09DB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30371C6C-EB0D-4D58-8A68-A86C5F1C52CE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2475191C-8B85-4BCE-BABA-5A78CCDEFCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="90" yWindow="2685" windowWidth="12915" windowHeight="10275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="73">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -114,20 +112,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ライブラリ設計</t>
-    <rPh sb="6" eb="8">
-      <t>セッケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>完了</t>
-    <rPh sb="0" eb="2">
-      <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>現在の日数(土日除く)</t>
     <rPh sb="0" eb="2">
       <t>ゲンザイ</t>
@@ -171,10 +155,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　ー　モデル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>今日の日付</t>
     <rPh sb="0" eb="2">
       <t>キョウ</t>
@@ -185,10 +165,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　ー　モーション</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>　ー　UI素材</t>
     <rPh sb="5" eb="7">
       <t>ソザイ</t>
@@ -284,73 +260,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　－　球と球の当たり判定</t>
-    <rPh sb="3" eb="4">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デッドライン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　球とカプセルの当たり判定</t>
-    <rPh sb="3" eb="4">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>真実のデッドライン</t>
-    <rPh sb="0" eb="2">
-      <t>シンジツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　カプセルとカプセルの当たり判定</t>
-    <rPh sb="13" eb="14">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　カプセルとマップの当たり判定</t>
-    <rPh sb="12" eb="13">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　物理挙動</t>
-    <rPh sb="3" eb="7">
-      <t>ブツリキョドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・プレイヤー</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -370,50 +279,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　―　ジャンプ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　―　ダッシュ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　―　ステップ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　―　ガード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　―　空中</t>
-    <rPh sb="3" eb="5">
-      <t>クウチュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　－　格闘攻撃</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　－　気弾攻撃</t>
-    <rPh sb="3" eb="4">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ダン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　－　コンボ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>　－　被弾</t>
     <rPh sb="3" eb="5">
       <t>ヒダン</t>
@@ -421,20 +286,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　－　必殺</t>
-    <rPh sb="3" eb="5">
-      <t>ヒッサツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　－　気力ため</t>
-    <rPh sb="3" eb="5">
-      <t>キリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>　－　死亡</t>
     <rPh sb="3" eb="5">
       <t>シボウ</t>
@@ -442,16 +293,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　－　競り合い</t>
-    <rPh sb="3" eb="4">
-      <t>セ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>　－　アニメーション実装</t>
     <rPh sb="10" eb="12">
       <t>ジッソウ</t>
@@ -466,23 +307,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　―　AI</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・キャラクター</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>　―　キャラ１</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　―　キャラ２</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　―　キャラ３</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -500,29 +329,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　ー　ブレンド有り再生</t>
-    <rPh sb="7" eb="8">
-      <t>アリ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>サイセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　ブレンド有り切り替え</t>
-    <rPh sb="7" eb="8">
-      <t>アリ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>　ー　再生速度調整</t>
     <rPh sb="3" eb="5">
       <t>サイセイ</t>
@@ -536,58 +342,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・カメラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　移動</t>
-  </si>
-  <si>
-    <t>　ー　回転</t>
-  </si>
-  <si>
-    <t>　ー　イージング</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　追随</t>
-  </si>
-  <si>
-    <t>　ー　必殺技演出</t>
-    <rPh sb="3" eb="8">
-      <t>ヒッサツワザエンシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　競り合い演出</t>
-    <rPh sb="3" eb="4">
-      <t>セ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>エンシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　勝利敗北演出</t>
-    <rPh sb="3" eb="9">
-      <t>ショウリハイボクエンシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・マップ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>　－　マップ設計</t>
-  </si>
-  <si>
-    <t>　ー　配置データの保存</t>
   </si>
   <si>
     <t>　ー　配置データの読み込み</t>
@@ -624,20 +383,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　ー　モードセレクト画面</t>
-    <rPh sb="10" eb="12">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　キャラセレクト画面</t>
-    <rPh sb="10" eb="12">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>　ー　バトル画面</t>
     <rPh sb="6" eb="8">
       <t>ガメン</t>
@@ -665,9 +410,6 @@
     <t>　ー　プレイヤー操作</t>
   </si>
   <si>
-    <t>　ー　カメラ操作</t>
-  </si>
-  <si>
     <t>・エフェクト</t>
   </si>
   <si>
@@ -677,13 +419,86 @@
     <t>　ー　エフェクト停止</t>
   </si>
   <si>
-    <t>　ー　座標回転と拡大</t>
-  </si>
-  <si>
     <t>　ー　エフェクト実装</t>
   </si>
   <si>
     <t>・ビルドテスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未完</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　－　呪文攻撃</t>
+    <rPh sb="3" eb="5">
+      <t>ジュモン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　－　武器攻撃</t>
+    <rPh sb="3" eb="5">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　ー　クリア画面</t>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　ー　ゲームオーバー画面</t>
+    <rPh sb="10" eb="12">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　―　ザコ敵</t>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　―　ボス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　－　プレイヤーと敵の当たり判定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　－　プレイヤーと回復ポイントの当たり判定</t>
+    <rPh sb="9" eb="11">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　ー　キャラドット絵素材</t>
+    <rPh sb="9" eb="10">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソザイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -754,12 +569,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -800,8 +609,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -824,54 +639,29 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1152,11 +942,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
-    <col min="2" max="2" width="37.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.375" customWidth="1"/>
     <col min="4" max="4" width="12.625" customWidth="1"/>
     <col min="5" max="7" width="21" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
@@ -1184,12 +974,12 @@
       <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="12" t="s">
         <v>5</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C83)</f>
-        <v>156</v>
+        <f>SUM(C3:C55)</f>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1197,18 +987,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="13" t="s">
         <v>8</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E83,"完了",C3:C83)</f>
-        <v>31</v>
+        <f>SUMIF(E3:E55,"完了",C3:C55)</f>
+        <v>0</v>
       </c>
       <c r="K3" t="s">
         <v>9</v>
@@ -1219,70 +1009,66 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="G4" s="14" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="9">
-        <v>8</v>
-      </c>
-      <c r="D4" s="9">
-        <v>8</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>13</v>
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>474</v>
+        <v>-2</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J4" s="3">
         <f ca="1" xml:space="preserve"> H3 / H4</f>
-        <v>6.5400843881856546E-2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>661</v>
+        <v>-2</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
-        <v>4.6898638426626324E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="9">
+        <v>2</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1">
+        <f>DATE(2026,7,25)</f>
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="G5" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="1">
-        <f>DATE(2024,9,30)</f>
-        <v>45565</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="B6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="9">
-        <v>2</v>
-      </c>
-      <c r="D6" s="9">
-        <v>2</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
@@ -1290,23 +1076,23 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="B7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="10">
-        <v>5</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10" t="s">
+      <c r="B7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8" t="s">
@@ -1315,10 +1101,10 @@
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8" t="s">
@@ -1326,243 +1112,180 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="I11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="8">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="B11" s="8" t="s">
+      <c r="K11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="8">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8" t="s">
-        <v>7</v>
+      <c r="L11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="B12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="10">
-        <v>5</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" t="s">
-        <v>28</v>
-      </c>
+      <c r="B12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0.5</v>
+      </c>
       <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="G13" s="13" t="s">
-        <v>30</v>
+      <c r="E13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="H13" s="1">
-        <f>DATE(2024,12,20)</f>
-        <v>45646</v>
+        <f>DATE(2026,8,20)</f>
+        <v>46254</v>
       </c>
       <c r="I13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H13)</f>
-        <v>-415</v>
+        <v>21</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>-0.30120481927710846</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>-580</v>
+        <v>28</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>-0.21551724137931033</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="9">
-        <v>2</v>
-      </c>
-      <c r="D14" s="9">
-        <v>2</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="1">
-        <f>DATE(2025,1,17)</f>
-        <v>45674</v>
-      </c>
-      <c r="I14" s="2">
-        <f ca="1">NETWORKDAYS(TODAY(),H14)</f>
-        <v>-395</v>
-      </c>
-      <c r="J14" s="3">
-        <f ca="1">($H$2 - $H$3) / I14</f>
-        <v>-0.31645569620253167</v>
-      </c>
-      <c r="K14">
-        <f t="shared" ref="K14:K15" ca="1" si="0">_xlfn.DAYS(H14,$H$6)</f>
-        <v>-552</v>
-      </c>
-      <c r="L14" s="3">
-        <f ca="1">($H$2 - $H$3) / K14</f>
-        <v>-0.22644927536231885</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" spans="1:12">
       <c r="B15" s="9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C15" s="9">
-        <v>2</v>
-      </c>
-      <c r="D15" s="9">
-        <v>2</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="1">
-        <f>DATE(2025,2,3)</f>
-        <v>45691</v>
-      </c>
-      <c r="I15" s="2">
-        <f ca="1">NETWORKDAYS(TODAY(),H15)</f>
-        <v>-384</v>
-      </c>
-      <c r="J15" s="3">
-        <f ca="1">($H$2 - $H$3) / I15</f>
-        <v>-0.32552083333333331</v>
-      </c>
-      <c r="K15">
-        <f t="shared" ca="1" si="0"/>
-        <v>-535</v>
-      </c>
-      <c r="L15" s="3">
-        <f ca="1">($H$2 - $H$3) / K15</f>
-        <v>-0.23364485981308411</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C16" s="9">
-        <v>2</v>
-      </c>
-      <c r="D16" s="9">
-        <v>2</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="3"/>
-      <c r="L16" s="3"/>
+        <v>63</v>
+      </c>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="8">
-        <v>2</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8" t="s">
+      <c r="B17" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="10">
+        <v>1</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="9">
-        <v>2</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="B18" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="10">
         <v>1</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>12</v>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="B19" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="8">
+        <v>1</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="9">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9">
-        <v>1</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>12</v>
+      <c r="B20" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="9">
+      <c r="B21" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="8">
         <v>0.5</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9" t="s">
-        <v>12</v>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="10" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C22" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="10" t="s">
@@ -1570,56 +1293,48 @@
       </c>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8" t="s">
-        <v>7</v>
-      </c>
+      <c r="B23" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="8">
-        <v>2</v>
-      </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8" t="s">
+      <c r="B24" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="17">
+        <v>1</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="8">
-        <v>1</v>
-      </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8" t="s">
+      <c r="B25" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="8">
-        <v>2</v>
-      </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8" t="s">
-        <v>7</v>
-      </c>
+      <c r="B26" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C27" s="8">
         <v>0.5</v>
@@ -1630,656 +1345,317 @@
       </c>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="10">
-        <v>4</v>
-      </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="B28" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="8">
-        <v>2</v>
-      </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8" t="s">
-        <v>7</v>
+      <c r="B29" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="10">
-        <v>4</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10" t="s">
-        <v>7</v>
+      <c r="B30" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="2:5">
-      <c r="B31" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="10">
-        <v>6</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="B31" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="10">
-        <v>8</v>
-      </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
+      <c r="B32" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="8">
+        <v>1</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
       <c r="B33" s="8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C33" s="8">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="2:5">
+    <row r="34" spans="2:7">
       <c r="B34" s="8" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C34" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="8">
-        <v>1</v>
-      </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="10">
-        <v>4</v>
-      </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5">
-      <c r="B37" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-    </row>
-    <row r="38" spans="2:5">
-      <c r="B38" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="11">
-        <v>20</v>
-      </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" s="8">
-        <v>1</v>
-      </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5">
+    <row r="35" spans="2:7">
+      <c r="B35" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+    </row>
+    <row r="41" spans="2:7">
       <c r="B41" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C41" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="2:5">
+    <row r="42" spans="2:7">
       <c r="B42" s="8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C42" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="2:5">
-      <c r="B43" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-    </row>
-    <row r="44" spans="2:5">
-      <c r="B44" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="9">
+    <row r="43" spans="2:7">
+      <c r="B43" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="8">
         <v>1</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D47" s="8"/>
+      <c r="E47" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="11">
         <v>1</v>
       </c>
-      <c r="E44" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5">
-      <c r="B45" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" s="9">
-        <v>1</v>
-      </c>
-      <c r="D45" s="9">
-        <v>1</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5">
-      <c r="B46" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C46" s="9">
-        <v>1</v>
-      </c>
-      <c r="D46" s="9">
-        <v>1</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5">
-      <c r="B47" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="9">
+      <c r="D50" s="11"/>
+      <c r="E50" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" s="8">
         <v>0.5</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D52" s="8"/>
+      <c r="E52" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7">
+      <c r="B53" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53" s="8">
         <v>0.5</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5">
-      <c r="B48" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-    </row>
-    <row r="49" spans="2:5">
-      <c r="B49" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" s="9">
-        <v>6</v>
-      </c>
-      <c r="D49" s="9">
-        <v>6</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5">
-      <c r="B50" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C50" s="9">
-        <v>1</v>
-      </c>
-      <c r="D50" s="9">
-        <v>1</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5">
-      <c r="B51" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="8">
-        <v>1</v>
-      </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5">
-      <c r="B52" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C52" s="9">
-        <v>1</v>
-      </c>
-      <c r="D52" s="9">
-        <v>1</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5">
-      <c r="B53" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C53" s="8">
-        <v>2</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="2:5">
+    <row r="54" spans="2:7">
       <c r="B54" s="8" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C54" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="2:5">
+    <row r="55" spans="2:7">
       <c r="B55" s="8" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C55" s="8">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5">
-      <c r="B56" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-    </row>
-    <row r="57" spans="2:5">
-      <c r="B57" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C57" s="8">
-        <v>1</v>
-      </c>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5">
-      <c r="B58" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C58" s="8">
-        <v>1</v>
-      </c>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5">
-      <c r="B59" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C59" s="8">
-        <v>1</v>
-      </c>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5">
-      <c r="B60" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C60" s="8">
-        <v>1</v>
-      </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5">
-      <c r="B61" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-    </row>
-    <row r="62" spans="2:5">
-      <c r="B62" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C62" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5">
-      <c r="B63" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C63" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5">
-      <c r="B64" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C64" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7">
-      <c r="B65" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C65" s="8">
-        <v>2</v>
-      </c>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G65" s="1"/>
-    </row>
-    <row r="66" spans="2:7">
-      <c r="B66" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="G66" s="1"/>
-    </row>
-    <row r="67" spans="2:7">
-      <c r="B67" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" s="1"/>
-    </row>
-    <row r="68" spans="2:7">
-      <c r="B68" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G68" s="1"/>
-    </row>
-    <row r="69" spans="2:7">
-      <c r="B69" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" s="8">
-        <v>1</v>
-      </c>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7">
-      <c r="B70" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C70" s="8">
-        <v>2</v>
-      </c>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="2:7">
-      <c r="B71" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C71" s="8">
-        <v>2</v>
-      </c>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7">
-      <c r="B72" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-    </row>
-    <row r="73" spans="2:7">
-      <c r="B73" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C73" s="8">
-        <v>1</v>
-      </c>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="2:7">
-      <c r="B74" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C74" s="8">
-        <v>1</v>
-      </c>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="2:7">
-      <c r="B75" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C75" s="8">
-        <v>1</v>
-      </c>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="2:7">
-      <c r="B76" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C76" s="12">
-        <v>4</v>
-      </c>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="2:7">
-      <c r="B77" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77" s="10">
-        <v>6</v>
-      </c>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="2:7">
-      <c r="B78" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-    </row>
-    <row r="79" spans="2:7">
-      <c r="B79" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C79" s="8">
-        <v>1</v>
-      </c>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="2:7">
-      <c r="B80" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C80" s="8">
-        <v>1</v>
-      </c>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5">
-      <c r="B81" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C81" s="10">
-        <v>4</v>
-      </c>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5">
-      <c r="B82" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C82" s="8">
-        <v>2</v>
-      </c>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5">
-      <c r="B83" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C83" s="8">
-        <v>2</v>
-      </c>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2291,6 +1667,62 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -2679,62 +2111,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2745,13 +2121,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/夏休みの課題/進捗コスト表.xlsx
+++ b/夏休みの課題/進捗コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Documents\GitHub\summer\夏休みの課題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2475191C-8B85-4BCE-BABA-5A78CCDEFCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CEB934-00AD-4048-B1A6-1158F740E197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="2685" windowWidth="12915" windowHeight="10275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7770" yWindow="3465" windowWidth="12915" windowHeight="10275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="74">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -498,6 +498,13 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>ソザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　―　回復処理</t>
+    <rPh sb="3" eb="7">
+      <t>カイフクショリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -942,7 +949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -978,8 +985,8 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C55)</f>
-        <v>35</v>
+        <f>SUM(C3:C56)</f>
+        <v>35.5</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -997,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E55,"完了",C3:C55)</f>
+        <f>SUMIF(E3:E56,"完了",C3:C56)</f>
         <v>0</v>
       </c>
       <c r="K3" t="s">
@@ -1177,7 +1184,7 @@
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>1.6666666666666667</v>
+        <v>1.6904761904761905</v>
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
@@ -1185,7 +1192,7 @@
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>1.25</v>
+        <v>1.2678571428571428</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1210,31 +1217,31 @@
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="9" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C16" s="9">
         <v>0.5</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="10">
-        <v>1</v>
-      </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="10" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C18" s="10">
         <v>1</v>
@@ -1245,79 +1252,79 @@
       </c>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="10">
+        <v>1</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C20" s="8">
         <v>1</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="10" t="s">
+      <c r="D20" s="8"/>
+      <c r="E20" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C21" s="10">
         <v>0.5</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
-      <c r="B21" s="8" t="s">
+      <c r="D21" s="10"/>
+      <c r="E21" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C22" s="8">
         <v>0.5</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="10" t="s">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C23" s="10">
         <v>1</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="9" t="s">
+      <c r="D23" s="10"/>
+      <c r="E23" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="17">
-        <v>1</v>
-      </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17" t="s">
-        <v>7</v>
-      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C25" s="17">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D25" s="17"/>
       <c r="E25" s="17" t="s">
@@ -1325,48 +1332,48 @@
       </c>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="8" t="s">
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C28" s="8">
         <v>0.5</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
-      <c r="B28" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="9">
-        <v>0.5</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C29" s="9"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="9" t="s">
-        <v>63</v>
-      </c>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30" s="9">
         <v>0.5</v>
@@ -1378,71 +1385,71 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-    </row>
-    <row r="32" spans="2:5">
-      <c r="B32" s="8" t="s">
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C33" s="8">
         <v>1</v>
-      </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="8">
-        <v>1.5</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:5">
       <c r="B34" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" s="8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="9" t="s">
+    <row r="35" spans="2:5">
+      <c r="B35" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="8" t="s">
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="C36" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="C37" s="8">
         <v>0.5</v>
@@ -1452,9 +1459,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
+    <row r="38" spans="2:5">
       <c r="B38" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" s="8">
         <v>0.5</v>
@@ -1464,9 +1471,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="2:7">
+    <row r="39" spans="2:5">
       <c r="B39" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C39" s="8">
         <v>0.5</v>
@@ -1476,29 +1483,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="9" t="s">
+    <row r="40" spans="2:5">
+      <c r="B40" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="B41" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-    </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="8" t="s">
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+    </row>
+    <row r="42" spans="2:5">
+      <c r="B42" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="C41" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="C42" s="8">
         <v>0.5</v>
@@ -1508,9 +1515,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="2:7">
+    <row r="43" spans="2:5">
       <c r="B43" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C43" s="8">
         <v>0.5</v>
@@ -1520,69 +1527,68 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="2:7">
+    <row r="44" spans="2:5">
       <c r="B44" s="8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C44" s="8">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:5">
       <c r="B45" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45" s="8">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
-      <c r="B46" s="9" t="s">
+    <row r="46" spans="2:5">
+      <c r="B46" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5">
+      <c r="B47" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-    </row>
-    <row r="47" spans="2:7">
-      <c r="B47" s="8" t="s">
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+    </row>
+    <row r="48" spans="2:5">
+      <c r="B48" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C48" s="8">
         <v>1</v>
-      </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7">
-      <c r="B48" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="8">
-        <v>0.5</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G48" s="1"/>
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C49" s="8">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="8" t="s">
@@ -1591,41 +1597,42 @@
       <c r="G49" s="1"/>
     </row>
     <row r="50" spans="2:7">
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C51" s="11">
         <v>1</v>
       </c>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="2:7">
-      <c r="B51" s="9" t="s">
+      <c r="D51" s="11"/>
+      <c r="E51" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-    </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8" t="s">
-        <v>7</v>
-      </c>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C53" s="8">
         <v>0.5</v>
@@ -1637,7 +1644,7 @@
     </row>
     <row r="54" spans="2:7">
       <c r="B54" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C54" s="8">
         <v>0.5</v>
@@ -1649,13 +1656,25 @@
     </row>
     <row r="55" spans="2:7">
       <c r="B55" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C55" s="8">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1667,62 +1686,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -2111,6 +2074,62 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2121,17 +2140,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2150,6 +2158,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>

--- a/夏休みの課題/進捗コスト表.xlsx
+++ b/夏休みの課題/進捗コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Documents\GitHub\summer\夏休みの課題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CEB934-00AD-4048-B1A6-1158F740E197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981D1150-EA33-4D05-AA6D-E60D92585E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7770" yWindow="3465" windowWidth="12915" windowHeight="10275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1175,8 +1175,8 @@
         <v>26</v>
       </c>
       <c r="H13" s="1">
-        <f>DATE(2026,8,20)</f>
-        <v>46254</v>
+        <f>DATE(2026,8,23)</f>
+        <v>46257</v>
       </c>
       <c r="I13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H13)</f>
@@ -1188,11 +1188,11 @@
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>1.2678571428571428</v>
+        <v>1.1833333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1686,6 +1686,62 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -2074,62 +2130,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2140,6 +2140,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2158,17 +2169,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>

--- a/夏休みの課題/進捗コスト表.xlsx
+++ b/夏休みの課題/進捗コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Documents\GitHub\summer\夏休みの課題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981D1150-EA33-4D05-AA6D-E60D92585E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C261AC1-65F4-4BAF-A07D-A9974790C408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="210" windowWidth="12915" windowHeight="10275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -407,9 +407,6 @@
     <t>　ー　画面遷移</t>
   </si>
   <si>
-    <t>　ー　プレイヤー操作</t>
-  </si>
-  <si>
     <t>・エフェクト</t>
   </si>
   <si>
@@ -506,6 +503,17 @@
     <rPh sb="3" eb="7">
       <t>カイフクショリ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -517,7 +525,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -536,13 +544,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
@@ -650,7 +651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -662,7 +663,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -949,7 +949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -981,12 +981,12 @@
       <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>5</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C56)</f>
-        <v>35.5</v>
+        <f>SUM(C3:C55)</f>
+        <v>36.5</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1000,12 +1000,12 @@
       <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>8</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E56,"完了",C3:C56)</f>
-        <v>0</v>
+        <f>SUMIF(E3:E55,"完了",C3:C55)</f>
+        <v>2.5</v>
       </c>
       <c r="K3" t="s">
         <v>9</v>
@@ -1021,7 +1021,7 @@
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="2">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="J4" s="3">
         <f ca="1" xml:space="preserve"> H3 / H4</f>
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
@@ -1041,21 +1041,21 @@
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
-        <v>0</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" s="9">
         <v>2</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>14</v>
       </c>
       <c r="H5" s="1">
@@ -1074,7 +1074,7 @@
       <c r="E6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="15" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="1">
@@ -1152,26 +1152,30 @@
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="9">
         <v>0.5</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="D12" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="9">
         <v>0.5</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="11" t="s">
         <v>26</v>
       </c>
       <c r="H13" s="1">
@@ -1184,7 +1188,7 @@
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>1.6904761904761905</v>
+        <v>1.6190476190476191</v>
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
@@ -1192,7 +1196,7 @@
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>1.1833333333333333</v>
+        <v>1.1333333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1210,14 +1214,16 @@
       <c r="C15" s="9">
         <v>0.5</v>
       </c>
-      <c r="D15" s="9"/>
+      <c r="D15" s="9">
+        <v>0.5</v>
+      </c>
       <c r="E15" s="9" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C16" s="9">
         <v>0.5</v>
@@ -1234,9 +1240,11 @@
       <c r="C17" s="9">
         <v>0.5</v>
       </c>
-      <c r="D17" s="9"/>
+      <c r="D17" s="9">
+        <v>0.5</v>
+      </c>
       <c r="E17" s="9" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -1246,14 +1254,16 @@
       <c r="C18" s="10">
         <v>1</v>
       </c>
-      <c r="D18" s="10"/>
+      <c r="D18" s="10">
+        <v>1</v>
+      </c>
       <c r="E18" s="10" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
@@ -1265,7 +1275,7 @@
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" s="8">
         <v>1</v>
@@ -1320,26 +1330,26 @@
       <c r="E24" s="9"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="16">
+        <v>2</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="17">
-        <v>1</v>
-      </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
-      <c r="B26" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17" t="s">
+      <c r="C26" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1380,7 +1390,7 @@
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="2:5">
@@ -1392,7 +1402,7 @@
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="2:5">
@@ -1517,7 +1527,7 @@
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C43" s="8">
         <v>0.5</v>
@@ -1529,7 +1539,7 @@
     </row>
     <row r="44" spans="2:5">
       <c r="B44" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C44" s="8">
         <v>0.5</v>
@@ -1610,25 +1620,24 @@
       <c r="G50" s="1"/>
     </row>
     <row r="51" spans="2:7">
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="11">
-        <v>1</v>
-      </c>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G51" s="1"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
     </row>
     <row r="52" spans="2:7">
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
+      <c r="C52" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="8" t="s">
@@ -1659,22 +1668,10 @@
         <v>61</v>
       </c>
       <c r="C55" s="8">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7">
-      <c r="B56" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1686,62 +1683,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -2130,6 +2071,62 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2140,17 +2137,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2169,6 +2155,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>

--- a/夏休みの課題/進捗コスト表.xlsx
+++ b/夏休みの課題/進捗コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Documents\GitHub\summer\夏休みの課題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C261AC1-65F4-4BAF-A07D-A9974790C408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519A3BCB-2550-498D-9B56-F302355049DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="210" windowWidth="12915" windowHeight="10275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="525" windowWidth="12915" windowHeight="10275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="H3">
         <f>SUMIF(E3:E55,"完了",C3:C55)</f>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="s">
         <v>9</v>
@@ -1026,22 +1026,22 @@
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="3">
         <f ca="1" xml:space="preserve"> H3 / H4</f>
-        <v>-2.5</v>
+        <v>1.75</v>
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
-        <v>-2.5</v>
+        <v>1.1666666666666667</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1171,9 +1171,11 @@
       <c r="C13" s="9">
         <v>0.5</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="9">
+        <v>0.5</v>
+      </c>
       <c r="E13" s="9" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>26</v>
@@ -1184,19 +1186,19 @@
       </c>
       <c r="I13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H13)</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>1.6190476190476191</v>
+        <v>1.736842105263158</v>
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>1.1333333333333333</v>
+        <v>1.2692307692307692</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1228,9 +1230,11 @@
       <c r="C16" s="9">
         <v>0.5</v>
       </c>
-      <c r="D16" s="9"/>
+      <c r="D16" s="9">
+        <v>0.5</v>
+      </c>
       <c r="E16" s="9" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -1683,6 +1687,62 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -2071,62 +2131,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2137,6 +2141,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2155,17 +2170,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>

--- a/夏休みの課題/進捗コスト表.xlsx
+++ b/夏休みの課題/進捗コスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KubotaNanato\Documents\GitHub\summer\夏休みの課題\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naato\OneDrive\ドキュメント\GitHub\summer\夏休みの課題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519A3BCB-2550-498D-9B56-F302355049DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A98766C-00BB-4555-8405-B429AB2246BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="525" windowWidth="12915" windowHeight="10275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4245" yWindow="2820" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -396,9 +396,6 @@
   <si>
     <t>・UX</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　カーソル移動</t>
   </si>
   <si>
     <t>　ー　決定処理</t>
@@ -949,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -985,8 +982,8 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C55)</f>
-        <v>36.5</v>
+        <f>SUM(C3:C54)</f>
+        <v>35.5</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1004,8 +1001,8 @@
         <v>8</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E55,"完了",C3:C55)</f>
-        <v>3.5</v>
+        <f>SUMIF(E3:E54,"完了",C3:C54)</f>
+        <v>9.5</v>
       </c>
       <c r="K3" t="s">
         <v>9</v>
@@ -1026,34 +1023,34 @@
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="3">
         <f ca="1" xml:space="preserve"> H3 / H4</f>
-        <v>1.75</v>
+        <v>0.95</v>
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
-        <v>1.1666666666666667</v>
+        <v>0.73076923076923073</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" s="9">
         <v>2</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>14</v>
@@ -1079,7 +1076,7 @@
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1113,9 +1110,11 @@
       <c r="C9" s="8">
         <v>1</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
       <c r="E9" s="8" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1152,7 +1151,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="9">
         <v>0.5</v>
@@ -1161,12 +1160,12 @@
         <v>0.5</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="9">
         <v>0.5</v>
@@ -1175,7 +1174,7 @@
         <v>0.5</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>26</v>
@@ -1186,19 +1185,19 @@
       </c>
       <c r="I13" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H13)</f>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>1.736842105263158</v>
+        <v>2.3636363636363638</v>
       </c>
       <c r="K13">
         <f ca="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>1.2692307692307692</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1220,21 +1219,21 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="C16" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -1248,7 +1247,7 @@
         <v>0.5</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -1262,12 +1261,12 @@
         <v>1</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="10">
         <v>1</v>
@@ -1279,7 +1278,7 @@
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="8">
         <v>1</v>
@@ -1335,7 +1334,7 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25" s="16">
         <v>2</v>
@@ -1347,7 +1346,7 @@
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" s="16">
         <v>2.5</v>
@@ -1394,7 +1393,7 @@
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="2:5">
@@ -1406,7 +1405,7 @@
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="2:5">
@@ -1417,43 +1416,49 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="2:5">
+    <row r="33" spans="2:7">
       <c r="B33" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="8">
         <v>1</v>
       </c>
-      <c r="D33" s="8"/>
+      <c r="D33" s="8">
+        <v>1</v>
+      </c>
       <c r="E33" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
       <c r="B34" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="8">
         <v>1.5</v>
       </c>
-      <c r="D34" s="8"/>
+      <c r="D34" s="8">
+        <v>1</v>
+      </c>
       <c r="E34" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="8">
         <v>1</v>
       </c>
-      <c r="D35" s="8"/>
+      <c r="D35" s="8">
+        <v>2</v>
+      </c>
       <c r="E35" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36" s="9" t="s">
         <v>44</v>
       </c>
@@ -1461,7 +1466,7 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="2:5">
+    <row r="37" spans="2:7">
       <c r="B37" s="8" t="s">
         <v>45</v>
       </c>
@@ -1473,7 +1478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="2:5">
+    <row r="38" spans="2:7">
       <c r="B38" s="8" t="s">
         <v>46</v>
       </c>
@@ -1485,7 +1490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="2:5">
+    <row r="39" spans="2:7">
       <c r="B39" s="8" t="s">
         <v>47</v>
       </c>
@@ -1497,7 +1502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="2:5">
+    <row r="40" spans="2:7">
       <c r="B40" s="8" t="s">
         <v>48</v>
       </c>
@@ -1509,7 +1514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="2:5">
+    <row r="41" spans="2:7">
       <c r="B41" s="9" t="s">
         <v>49</v>
       </c>
@@ -1517,7 +1522,7 @@
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
     </row>
-    <row r="42" spans="2:5">
+    <row r="42" spans="2:7">
       <c r="B42" s="8" t="s">
         <v>50</v>
       </c>
@@ -1529,9 +1534,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="2:5">
+    <row r="43" spans="2:7">
       <c r="B43" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C43" s="8">
         <v>0.5</v>
@@ -1541,9 +1546,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="2:5">
+    <row r="44" spans="2:7">
       <c r="B44" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C44" s="8">
         <v>0.5</v>
@@ -1553,7 +1558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="2:5">
+    <row r="45" spans="2:7">
       <c r="B45" s="8" t="s">
         <v>51</v>
       </c>
@@ -1565,7 +1570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="2:5">
+    <row r="46" spans="2:7">
       <c r="B46" s="8" t="s">
         <v>52</v>
       </c>
@@ -1577,7 +1582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="2:5">
+    <row r="47" spans="2:7">
       <c r="B47" s="9" t="s">
         <v>53</v>
       </c>
@@ -1585,51 +1590,53 @@
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
     </row>
-    <row r="48" spans="2:5">
+    <row r="48" spans="2:7">
       <c r="B48" s="8" t="s">
         <v>54</v>
       </c>
       <c r="C48" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8" t="s">
         <v>7</v>
       </c>
+      <c r="G48" s="1"/>
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="8" t="s">
         <v>55</v>
       </c>
       <c r="C49" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D49" s="8"/>
+        <v>1.5</v>
+      </c>
+      <c r="D49" s="8">
+        <v>1.5</v>
+      </c>
       <c r="E49" s="8" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="G49" s="1"/>
     </row>
     <row r="50" spans="2:7">
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C50" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G50" s="1"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
     </row>
     <row r="51" spans="2:7">
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
+      <c r="C51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="8" t="s">
@@ -1660,22 +1667,10 @@
         <v>60</v>
       </c>
       <c r="C54" s="8">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7">
-      <c r="B55" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1743,6 +1738,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -2131,15 +2135,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
   <ds:schemaRefs>
@@ -2152,6 +2147,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2168,12 +2171,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>